--- a/VerveStacks_USA/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_USA/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0309201D-0840-497D-855B-D34B2346893F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{512BF946-D072-4DCB-B064-5DA9C580DA86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -599,10 +599,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>SaD,RaD,RaP,WaD,FaP,SaP,FaD,WaP</t>
+    <t>FaP,SaP,FaD,SaD,WaP,RaD,WaD,RaP</t>
   </si>
   <si>
-    <t>FaP,SaP,SaN,WaN,WaP,FaN,RaP,RaN</t>
+    <t>RaP,FaP,SaP,RaN,FaN,SaN,WaN,WaP</t>
   </si>
 </sst>
 </file>
@@ -24258,7 +24258,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71115C10-A7CE-4D3D-A4BB-4C0B2A3705D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31338117-B162-4566-8E72-819B6A72CC6F}">
   <dimension ref="A9:AN12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24498,7 +24498,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0399FB28-100C-49AC-876F-A4F0DCAE6A9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EF56D6E-7157-4513-B532-D458AEB60B68}">
   <dimension ref="A9:AN34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_USA/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_USA/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{512BF946-D072-4DCB-B064-5DA9C580DA86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5FA73FE-C76A-4110-838C-974A16922361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -599,10 +599,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaP,SaP,FaD,SaD,WaP,RaD,WaD,RaP</t>
+    <t>SaD,FaD,WaP,FaP,SaP,WaD,RaD,RaP</t>
   </si>
   <si>
-    <t>RaP,FaP,SaP,RaN,FaN,SaN,WaN,WaP</t>
+    <t>FaP,SaP,RaP,RaN,WaP,SaN,WaN,FaN</t>
   </si>
 </sst>
 </file>
@@ -24258,7 +24258,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31338117-B162-4566-8E72-819B6A72CC6F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8622224-24D1-4AA1-BF9C-EF33DCB2404F}">
   <dimension ref="A9:AN12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24498,7 +24498,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EF56D6E-7157-4513-B532-D458AEB60B68}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4BC670B-8FC3-4F7B-8DE6-4AEBBC130416}">
   <dimension ref="A9:AN34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_USA/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_USA/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5FA73FE-C76A-4110-838C-974A16922361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{121AD2A2-326D-4D2E-AF5F-A099EFE3EFC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -599,10 +599,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>SaD,FaD,WaP,FaP,SaP,WaD,RaD,RaP</t>
+    <t>SaD,FaP,SaP,RaD,RaP,WaD,WaP,FaD</t>
   </si>
   <si>
-    <t>FaP,SaP,RaP,RaN,WaP,SaN,WaN,FaN</t>
+    <t>FaP,SaP,FaN,RaN,RaP,SaN,WaN,WaP</t>
   </si>
 </sst>
 </file>
@@ -24258,7 +24258,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8622224-24D1-4AA1-BF9C-EF33DCB2404F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01EE1CF-F4EE-4DC9-9A2C-25895DBC3AD7}">
   <dimension ref="A9:AN12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24498,7 +24498,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4BC670B-8FC3-4F7B-8DE6-4AEBBC130416}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7139C85F-37E6-43AD-AD8E-238463809336}">
   <dimension ref="A9:AN34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
